--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>24 de julio de 2026</t>
+          <t>29 de julio de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>

--- a/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
+++ b/administrador/pagado_emitidido/pagado_emitido_reclutas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>29 de julio de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -478,22 +478,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JOSE ANTEMIO OLIVA SANTOS</t>
+          <t>OSCAR RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>5863.45</v>
+        <v>2396.76</v>
       </c>
       <c r="H4" t="n">
-        <v>1160.7</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7024.15</v>
+        <v>2396.76</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -502,16 +502,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>47128.14</v>
+        <v>26364.37</v>
       </c>
       <c r="M4" t="n">
-        <v>47128.14</v>
+        <v>26364.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>118915</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GERARDO DANIEL BARAJAS TORRES</t>
+          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1599.61</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1599.61</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -545,53 +545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>49020.81</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>118915</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HUMBERTO EMMANUEL SANDOVAL MOLINS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>49140.03</v>
-      </c>
-      <c r="M6" t="n">
-        <v>49140.03</v>
+        <v>49020.81</v>
       </c>
     </row>
   </sheetData>
